--- a/data/trans_orig/IP3109_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP3109_R-Estudios-trans_orig.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81553</t>
+          <t>81231</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76597</t>
+          <t>76099</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160168</t>
+          <t>159737</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164523</t>
+          <t>164526</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>591</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>381735</t>
+          <t>381671</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>387282</t>
+          <t>387234</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,82 +1091,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>445706</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>442263</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>447052</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>99,7%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1252</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>831064</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>826941</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>833634</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>99,84%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>445706</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>441970</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>447052</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>831064</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>826937</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>833206</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,77 +1204,77 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4789</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>3906</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>8029</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1346</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5082</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3906</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1764</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>8033</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>152085</t>
+          <t>152670</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>140011</t>
+          <t>140273</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>295085</t>
+          <t>295098</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>300400</t>
+          <t>300401</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>621017</t>
+          <t>621727</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>628319</t>
+          <t>628439</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,82 +1777,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>99,7%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>667638</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>664019</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>669637</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1936</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1293350</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>1287294</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>1297123</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>98,94%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>99,69%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>667638</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>663774</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>669578</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1936</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1293350</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1288230</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1297188</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>99,01%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>8573</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,82 +1890,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3190</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1191</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6809</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>7778</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>13834</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3190</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1250</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7054</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>7778</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>3940</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>12898</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82449</t>
+          <t>82288</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87253</t>
+          <t>87258</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78233</t>
+          <t>78959</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>163302</t>
+          <t>162830</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>169201</t>
+          <t>169129</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>742</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>397629</t>
+          <t>398084</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>405524</t>
+          <t>405746</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>437448</t>
+          <t>438359</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>445814</t>
+          <t>445763</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>838929</t>
+          <t>839807</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>849876</t>
+          <t>849814</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9667</t>
+          <t>8756</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16523</t>
+          <t>15645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>143256</t>
+          <t>143419</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150200</t>
+          <t>150204</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>150433</t>
+          <t>149759</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>296932</t>
+          <t>296618</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>303386</t>
+          <t>303377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7548</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>630524</t>
+          <t>630783</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>640821</t>
+          <t>641741</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>672311</t>
+          <t>672314</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>680719</t>
+          <t>680698</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1305823</t>
+          <t>1306870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1319500</t>
+          <t>1320132</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>9671</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23980</t>
+          <t>22933</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49336</t>
+          <t>49376</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116181</t>
+          <t>115862</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>421774</t>
+          <t>422708</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>429426</t>
+          <t>429104</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>448400</t>
+          <t>448755</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>872841</t>
+          <t>872937</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>880620</t>
+          <t>880678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>10339</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>146448</t>
+          <t>146591</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>152010</t>
+          <t>152003</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>154066</t>
+          <t>154777</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>160407</t>
+          <t>160402</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>303131</t>
+          <t>303858</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>311144</t>
+          <t>311314</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>641</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>721</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10636</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>623141</t>
+          <t>623967</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>633248</t>
+          <t>633158</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>671670</t>
+          <t>671595</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>678192</t>
+          <t>678189</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1298837</t>
+          <t>1298866</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1310327</t>
+          <t>1310047</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15009</t>
+          <t>14183</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18835</t>
+          <t>18806</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38348</t>
+          <t>37747</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48216</t>
+          <t>48511</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35982</t>
+          <t>36281</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48290</t>
+          <t>49039</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78079</t>
+          <t>77403</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95808</t>
+          <t>94046</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>84,36%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5188</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15351</t>
+          <t>15952</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21798</t>
+          <t>21499</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15670</t>
+          <t>17432</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33399</t>
+          <t>34075</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>378653</t>
+          <t>378672</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>406660</t>
+          <t>406227</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>413648</t>
+          <t>414042</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>442709</t>
+          <t>443598</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>799402</t>
+          <t>800875</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>841298</t>
+          <t>842867</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44347</t>
+          <t>44780</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72354</t>
+          <t>72335</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62541</t>
+          <t>61652</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91602</t>
+          <t>91208</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>114960</t>
+          <t>113391</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>156856</t>
+          <t>155383</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117267</t>
+          <t>116327</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131796</t>
+          <t>131109</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>149348</t>
+          <t>149596</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165664</t>
+          <t>166500</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>272316</t>
+          <t>271344</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>293860</t>
+          <t>293407</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,64%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14390</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28919</t>
+          <t>29859</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>14639</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31791</t>
+          <t>31543</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33464</t>
+          <t>33917</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55008</t>
+          <t>55980</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>544490</t>
+          <t>544633</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>576962</t>
+          <t>576824</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>610647</t>
+          <t>612287</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>648538</t>
+          <t>648671</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1166731</t>
+          <t>1167462</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1215910</t>
+          <t>1215699</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,14%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73930</t>
+          <t>74068</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106402</t>
+          <t>106259</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95631</t>
+          <t>95498</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133522</t>
+          <t>131882</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>179151</t>
+          <t>179362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>228330</t>
+          <t>227599</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3109_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP3109_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,74 +723,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>79055</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>76401</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>80250</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>95,2%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>84213</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>81231</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>81168</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>84867</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>99,23%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>95,64%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>79055</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>76099</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>80250</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>94,83%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>244</t>
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>159737</t>
+          <t>159578</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164526</t>
+          <t>164524</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1195</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3849</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3636</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3699</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1195</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4151</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>80250</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>80250</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>80250</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>84867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>84867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>84867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>80250</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>80250</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>80250</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,74 +1066,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>445706</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>442295</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>447052</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>99,7%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>98,94%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>580</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>385359</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>381671</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>387234</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>381516</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>387230</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>99,34%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>99,82%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>445706</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>442263</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>447052</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1252</t>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>826941</t>
+          <t>826994</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>833634</t>
+          <t>833618</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4757</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>2559</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6247</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6402</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1346</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4789</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>447052</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>447052</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>447052</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>584</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>387918</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>387918</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>387918</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>447052</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>447052</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>447052</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,74 +1409,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>142877</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>140277</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>143526</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>97,74%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>156140</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>152670</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>153145</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>157515</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>99,13%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>96,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>97,23%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>142877</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>140273</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>143526</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>97,73%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>440</t>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>295098</t>
+          <t>295717</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>300401</t>
+          <t>300399</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3249</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>1375</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4845</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4370</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,87%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>3253</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>143526</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>143526</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>143526</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>157515</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>157515</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>157515</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>143526</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>143526</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>143526</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,74 +1752,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>667638</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>663808</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>669598</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>98,95%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>933</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>625712</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>621727</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>628439</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>621572</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>628395</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>99,27%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>99,7%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>667638</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>664019</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>669637</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>98,98%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1936</t>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1287294</t>
+          <t>1288013</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1297123</t>
+          <t>1297330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3190</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7020</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>4588</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8573</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8728</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3190</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1191</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6809</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>670828</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>670828</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>670828</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>940</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>630300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>630300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>630300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1008</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>670828</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>670828</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>670828</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>81344</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>78876</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>81951</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96,25%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>85751</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>82288</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>87258</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>82027</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>87254</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>97,53%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>93,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>81344</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>78959</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>81951</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>162830</t>
+          <t>162951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>169129</t>
+          <t>169128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3075</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2169</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5632</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5893</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>2,47%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2992</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>743</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>81951</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>81951</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>81951</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>87920</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>87920</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>87920</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>81951</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>81951</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>81951</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>443224</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>438137</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>445808</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>582</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>402601</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>398084</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>405746</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>397723</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>405712</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>98,6%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>97,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>443224</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>438359</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>445763</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>839807</t>
+          <t>839176</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>849814</t>
+          <t>850178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3891</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8978</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>5735</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2590</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10252</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2624</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10613</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>3891</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1352</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>8756</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5638</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>16276</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>447115</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>447115</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>447115</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>591</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>408336</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>408336</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>408336</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>447115</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>447115</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>447115</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,74 +3012,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>153001</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>150387</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>153647</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>97,88%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>148371</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>143419</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>150204</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>144045</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>150203</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>98,37%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>95,08%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>95,5%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>99,58%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>153001</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>149759</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>153647</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>426</t>
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>296618</t>
+          <t>296882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>303377</t>
+          <t>303747</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>2462</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>629</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7414</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6788</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>3888</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>733</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>153647</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>153647</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>153647</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>150833</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>150833</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>150833</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>153647</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>153647</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>153647</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>677570</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>672493</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>680592</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>917</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>636722</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>630783</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>641741</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>630203</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>641399</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>98,4%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>97,48%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>677570</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>672314</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>680698</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1306870</t>
+          <t>1306703</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1320132</t>
+          <t>1320106</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5144</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2122</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10221</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>10367</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5348</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>16306</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5690</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>16886</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>5144</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>10400</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>9697</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22933</t>
+          <t>23100</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>682714</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>682714</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>682714</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>932</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>647089</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>647089</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>647089</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>682714</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>682714</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>682714</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,74 +3929,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>66531</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>52713</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>49376</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>49254</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>54098</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>97,44%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>91,27%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>91,05%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>66531</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>175</t>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>115862</t>
+          <t>115690</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4042,107 +4042,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>1385</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4722</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4844</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>2,56%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>8,95%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1385</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4939</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1385</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4767</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>66531</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>66531</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>66531</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>54098</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>54098</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>54098</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>66531</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>66531</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>66531</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>451155</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>448310</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>451868</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>99,84%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>640</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>426426</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>422708</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>429104</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>421867</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>429081</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>98,85%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>97,98%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>451155</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>448755</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>451868</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>99,84%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>872937</t>
+          <t>872920</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>880678</t>
+          <t>880370</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3558</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>4982</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2304</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8700</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>9541</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3113</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10339</t>
+          <t>10356</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>451868</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>451868</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>451868</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>648</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>431408</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>431408</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>431408</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>451868</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>451868</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>451868</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>158330</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>154653</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>160413</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>95,98%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>150191</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>146591</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>152003</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>146843</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>152014</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>98,39%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>96,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>158330</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>154777</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>160402</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>303858</t>
+          <t>303513</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>311314</t>
+          <t>311713</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -4733,67 +4733,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>2793</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6470</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>2453</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6053</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5801</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>1,61%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2793</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>721</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>6346</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>161123</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>161123</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>161123</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>152644</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>152644</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>152644</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>161123</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>161123</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>161123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>676016</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>671818</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>678182</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>98,87%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>99,8%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>629330</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>623967</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>633158</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>623491</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>633072</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>98,62%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>676016</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>671595</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>678189</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1298866</t>
+          <t>1298718</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1310047</t>
+          <t>1309896</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3506</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7704</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>8820</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4992</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14183</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5078</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>14659</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3506</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7927</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18806</t>
+          <t>18954</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>679522</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>679522</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>679522</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>957</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>638150</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>638150</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>638150</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>679522</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>679522</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>679522</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40437</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>33649</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>45378</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>76,01%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>63,25%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>85,29%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>44137</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>37747</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>48511</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>82,19%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>70,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>90,34%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42884</t>
+          <t>36080</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36281</t>
+          <t>30858</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49039</t>
+          <t>39982</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>87020</t>
+          <t>76517</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77403</t>
+          <t>68884</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94046</t>
+          <t>83002</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>83,75%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12766</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7825</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19554</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>23,99%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>14,71%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>36,75%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9562</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5188</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15952</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>17,81%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,66%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>29,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>9825</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8741</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21499</t>
+          <t>15047</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>24458</t>
+          <t>22591</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17432</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34075</t>
+          <t>30224</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,5%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53203</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53203</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53203</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>57780</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57780</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57780</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>111478</t>
+          <t>99108</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>111478</t>
+          <t>99108</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>111478</t>
+          <t>99108</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>398847</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>385218</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>410838</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>85,51%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>82,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>88,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>535</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>392436</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>378672</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>406227</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>87,01%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>83,96%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>90,07%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>429055</t>
+          <t>365742</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>414042</t>
+          <t>352729</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>443598</t>
+          <t>377596</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,22 +5950,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>821491</t>
+          <t>764588</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>800875</t>
+          <t>745598</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>842867</t>
+          <t>781671</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>67576</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>55585</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>81205</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>14,49%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>17,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>58571</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>44780</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>72335</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12,99%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,04%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>76195</t>
+          <t>58051</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61652</t>
+          <t>46197</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91208</t>
+          <t>71064</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,27 +6063,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>134767</t>
+          <t>125628</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>113391</t>
+          <t>108545</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>155383</t>
+          <t>144618</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>624</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451007</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451007</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451007</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>423793</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>423793</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>423793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>956258</t>
+          <t>890216</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>956258</t>
+          <t>890216</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>956258</t>
+          <t>890216</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>147866</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>138702</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>153376</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>88,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>83,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>92,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>124699</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>116327</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>131109</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>85,3%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>79,57%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>89,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>159238</t>
+          <t>125181</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>149596</t>
+          <t>116868</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>166500</t>
+          <t>131822</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>283936</t>
+          <t>273045</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>271344</t>
+          <t>261716</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>293407</t>
+          <t>282713</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18820</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>13310</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27984</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7,99%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>16,79%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>21487</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>15077</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>29859</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>14,7%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10,31%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>20,43%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21901</t>
+          <t>21959</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14639</t>
+          <t>15318</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31543</t>
+          <t>30272</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>43388</t>
+          <t>40780</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33917</t>
+          <t>31112</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55980</t>
+          <t>52109</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>587149</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>573183</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>602201</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>85,55%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>83,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>87,74%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>778</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>561272</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>544633</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>576824</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>86,23%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>83,67%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>88,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>631176</t>
+          <t>527002</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>612287</t>
+          <t>510202</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>648671</t>
+          <t>540079</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1192448</t>
+          <t>1114151</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1167462</t>
+          <t>1089375</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1215699</t>
+          <t>1135157</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,11%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>99163</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>84111</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>113129</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14,45%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12,26%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>16,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>89620</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>74068</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>106259</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>13,77%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>16,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>112993</t>
+          <t>89835</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95498</t>
+          <t>76758</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131882</t>
+          <t>106635</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>202613</t>
+          <t>188998</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>179362</t>
+          <t>167992</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>227599</t>
+          <t>213774</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>913</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>650892</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>650892</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>650892</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744169</t>
+          <t>616837</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744169</t>
+          <t>616837</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744169</t>
+          <t>616837</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1395061</t>
+          <t>1303149</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1395061</t>
+          <t>1303149</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1395061</t>
+          <t>1303149</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
